--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-14814</t>
+          <t>I-464345</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040107</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,22 +503,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JACOBO HUNTER</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-16.3971967</t>
+          <t>-16.4600496</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-71.5332068</t>
+          <t>-71.5566274</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle Rivero / Calle Santa Marta</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-177415</t>
+          <t>I-478443</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040107</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,22 +555,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JACOBO HUNTER</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-16.3964002</t>
+          <t>-16.4603201</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-71.5426316</t>
+          <t>-71.5561759</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Calle Beaterio / Calle la Recoleta</t>
+          <t>Calle 4 / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-177420</t>
+          <t>I-75854</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040102</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ALTO SELVA ALEGRE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.415389</t>
+          <t>-16.365769</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-71.5339601</t>
+          <t>-71.5243462</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Daniel Alcides Carrión</t>
+          <t>Avenida Francisco Mostajo / Calle Mariano Melgar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-197486</t>
+          <t>I-76275</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040117</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SACHACA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-16.4057806</t>
+          <t>-16.417342</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-71.5400894</t>
+          <t>-71.5833585</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Alameda Mario Vargas Llosa / Avenida Salaverry</t>
+          <t>Avenida Progreso / Pasaje San Martín</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-197504</t>
+          <t>I-77232</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040104</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,22 +711,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-16.4057349</t>
+          <t>-16.3601947</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-71.5401318</t>
+          <t>-71.5626588</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Alameda Mario Vargas Llosa / Avenida Salaverry</t>
+          <t>Avenida Tumbes / Sol Oeste</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-197506</t>
+          <t>I-78959</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040129</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-16.4057337</t>
+          <t>-16.4452971</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-71.540049</t>
+          <t>-71.5109901</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Alameda Mario Vargas Llosa / Avenida Salaverry</t>
+          <t>Primavera / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-214151</t>
+          <t>I-80956</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040112</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>PAUCARPATA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-16.4149176</t>
+          <t>-16.4109939</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-71.534333</t>
+          <t>-71.5134547</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Daniel Alcides Carrión / Calle San Rafael</t>
+          <t>Avenida los Incas / Calle Malecón Paucarpata / Calle Victoria</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-214152</t>
+          <t>I-82490</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040110</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,22 +867,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-16.4153245</t>
+          <t>-16.390434</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-71.5341481</t>
+          <t>-71.5163236</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Daniel Alcides Carrión / Calle Cabrera Valdez</t>
+          <t>Avenida Goyeneche / Calle Sánchez Trujillo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-329690</t>
+          <t>I-82981</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040112</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,27 +919,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>PAUCARPATA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-16.3970436</t>
+          <t>-16.4142869</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-71.5411805</t>
+          <t>-71.5095311</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida de la Marina</t>
+          <t>Calle Prolongación Avenida Jesús / Calle Industrial</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-357362</t>
+          <t>I-214151</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-16.41535</t>
+          <t>-16.4149176</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-71.5338424</t>
+          <t>-71.534333</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Daniel Alcides Carrión / Calle San Rafael</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-359854</t>
+          <t>I-351531</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040104</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,22 +1023,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-16.4052496</t>
+          <t>-16.3751623</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-71.532842</t>
+          <t>-71.5577353</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1055,12 +1055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-359858</t>
+          <t>I-308096</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040108</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LA JOYA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-16.4043665</t>
+          <t>-16.4458116</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-71.532921</t>
+          <t>-71.8255575</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle Nueva / Calle Víctor Lira</t>
+          <t>Avenida 28 de Julio / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-370610</t>
+          <t>I-408834</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040105</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHARACATO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-16.405589</t>
+          <t>-16.4654124</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-71.5400303</t>
+          <t>-71.4938768</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle la Merced</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-371242</t>
+          <t>I-329716</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040107</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1179,22 +1179,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JACOBO HUNTER</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-16.4103957</t>
+          <t>-16.4481823</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-71.5513085</t>
+          <t>-71.5661217</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-371861</t>
+          <t>I-329690</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-16.4080407</t>
+          <t>-16.3970436</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-71.5264541</t>
+          <t>-71.5411805</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida Venezuela</t>
+          <t>Avenida de la Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-371862</t>
+          <t>I-359854</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-16.4079531</t>
+          <t>-16.4052496</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-71.526234</t>
+          <t>-71.532842</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Venezuela / Calle Lorenzo Ballón</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>l-379878</t>
+          <t>I-479907</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040122</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1335,22 +1335,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SOCABAYA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-16.4055366</t>
+          <t>-16.4600118</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-71.5401445</t>
+          <t>-71.5469179</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Calle Sucre</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1367,12 +1367,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>l-469927</t>
+          <t>I-315015</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040108</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1387,22 +1387,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LA JOYA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-16.3970123</t>
+          <t>-16.6944388</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-71.5426428</t>
+          <t>-71.8806377</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l-474670</t>
+          <t>I-469927</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-16.4192364</t>
+          <t>-16.3970123</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-71.538601</t>
+          <t>-71.5426428</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle Beaterio / Avenida Zamacola</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>l-512108</t>
+          <t>I-78078</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040107</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1491,27 +1491,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JACOBO HUNTER</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-16.4190191</t>
+          <t>-16.4484409</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-71.5384247</t>
+          <t>-71.5663707</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>l-5511</t>
+          <t>I-511933</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040122</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1543,22 +1543,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SOCABAYA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-16.3978159</t>
+          <t>-16.4688735</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-71.5413394</t>
+          <t>-71.5514302</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Calle Francisco Bolognesi / Puente Bolognesi</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1575,12 +1575,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>l-5512</t>
+          <t>I-783960</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040122</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1595,22 +1595,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SOCABAYA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-16.39777434</t>
+          <t>-16.4579884</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-71.54143858</t>
+          <t>-71.5411931</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>l-5513</t>
+          <t>I-432161</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040122</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1647,27 +1647,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SOCABAYA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-16.39771786</t>
+          <t>-16.4672615</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-71.54157335</t>
+          <t>-71.551416</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle 1 / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>l-551402</t>
+          <t>I-511951</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040122</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,27 +1699,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SOCABAYA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-16.4191118</t>
+          <t>-16.465198</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-71.5386743</t>
+          <t>-71.5513946</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Principal / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>l-551403</t>
+          <t>I-84012</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1756,17 +1756,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-16.4191172</t>
+          <t>-16.4094426</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-71.5386822</t>
+          <t>-71.5336615</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Independencia / Tabada</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>l-75967</t>
+          <t>I-476749</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040117</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SACHACA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-16.419084</t>
+          <t>-16.4245836</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-71.5388411</t>
+          <t>-71.5873919</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Avenida Juan Vidaurrázaga</t>
+          <t>Avenida Progreso / Calle s / n</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>l-75971</t>
+          <t>I-472982</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040105</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1855,27 +1855,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHARACATO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-16.4193629</t>
+          <t>-16.4764167</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-71.5386583</t>
+          <t>-71.4922931</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Avenida Juan Vidaurrázaga</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>l-75978</t>
+          <t>I-371242</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-16.4191717</t>
+          <t>-16.4103957</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-71.5387851</t>
+          <t>-71.5513085</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Avenida Juan Vidaurrázaga</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>l-77148</t>
+          <t>I-474670</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-16.396951</t>
+          <t>-16.4192364</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-71.5426208</t>
+          <t>-71.538601</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida Zamacola / Calle Beaterio</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1991,12 +1991,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>l-77333</t>
+          <t>I-16978</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040110</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-16.4004842</t>
+          <t>-16.3926912</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-71.5405463</t>
+          <t>-71.5234521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Calle Consuelo / Calle Cruz Verde</t>
+          <t>Avenida Progreso / Calle Misti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>l-78509</t>
+          <t>I-2444</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040108</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2063,27 +2063,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LA JOYA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-16.4056874</t>
+          <t>-16.6224216</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-71.5400942</t>
+          <t>-71.8765728</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Alameda Mario Vargas Llosa / Avenida Salaverry / Calle Sucre / Calle la Merced</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>l-78510</t>
+          <t>I-566968</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040126</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2115,27 +2115,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>YANAHUARA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-16.4055852</t>
+          <t>-16.3724328</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-71.5402637</t>
+          <t>-71.5337133</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Avenida Salaverry</t>
+          <t>Avenida Chilina / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2147,12 +2147,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>l-790803</t>
+          <t>I-408742</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040126</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>YANAHUARA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-16.4190168</t>
+          <t>-16.3959692</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-71.538542</t>
+          <t>-71.5597961</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2199,12 +2199,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>l-790972</t>
+          <t>I-83927</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040126</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2219,27 +2219,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>YANAHUARA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-16.4190587</t>
+          <t>-16.3913501</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-71.5385996</t>
+          <t>-71.5431228</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Ejército / Avenida Emmel</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2251,12 +2251,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>l-790973</t>
+          <t>I-2447</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>040101</t>
+          <t>040108</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2271,498 +2271,30 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LA JOYA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-16.4191721</t>
+          <t>-16.6220388</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-71.5386433</t>
+          <t>-71.8785201</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>l-790974</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-16.4191616</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-71.5386497</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>l-81307</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-16.4062228</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-71.5297444</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Avenida Independencia</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>l-81308</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-16.4065258</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-71.5301115</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Avenida Independencia / Calle Juan de Dios Salazar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>l-82113</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-16.4191259</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-71.5389294</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Avenida Juan Vidaurrázaga</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>l-82120</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-16.4188968</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-71.5385179</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>l-82121</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-16.4190721</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-71.5387842</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>l-82122</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-16.4189294</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-71.5385654</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>l-83101</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-16.4054314</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-71.5330342</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Avenida Jorge Chávez / Calle 2 de Mayo</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>l-84012</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-16.4094426</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-71.5336615</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Avenida Independencia / Tabada</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
         <is>
           <t>040101</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Paisajista / Calle s / n</t>
+          <t>Avenida Paisajista / Calle 4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Primavera / Calle s / n</t>
+          <t>José Galvez / Primavera / Reynoso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida los Incas / Calle Malecón Paucarpata / Calle Victoria</t>
+          <t>Avenida los Incas / Calle Malecón Paucarpata / Calle Victoria / Prolongación Avenida Jesús</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle Prolongación Avenida Jesús / Calle Industrial</t>
+          <t>Calle Mariano Gonzales Prada / Prolongación Avenida Jesús</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Daniel Alcides Carrión / Calle San Rafael</t>
+          <t>Avenida Daniel Alcides Carrión / Calle San Rafael / Vía Exclusiva Daniel Alcides Carrión</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Aviación / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Characato / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle Beaterio / Avenida Zamacola</t>
+          <t>Avenida Zamacola / Calle Beaterio</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Juan Vidaurrázaga / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2295,6 +2295,266 @@
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>040101</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>I-2437</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>040104</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CERRO COLORADO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-16.3865776</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-71.5538504</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Avenida Prolongación Ejército / Circunvalación</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>040101</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>I-477887</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>040107</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>JACOBO HUNTER</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-16.4384415</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-71.5607491</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Avenida Las Américas / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>040101</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>I-2448</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>040108</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LA JOYA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-16.6217582</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-71.879947</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>040101</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>I-16980</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>040110</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-16.3933911</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-71.5225763</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Avenida Progreso / Avenida San Martín</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>040101</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>I-5468</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-16.4006537</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-71.550931</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Calle Los Jazmines / Las Orquídeas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>040101</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-464345</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>040107</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-16.4600496</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-478443</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>040107</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-16.4603201</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-75854</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>040102</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ALTO SELVA ALEGRE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-16.365769</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-76275</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>040117</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SACHACA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-16.417342</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-77232</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>040104</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-16.3601947</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-78959</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>040129</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-16.4452971</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-80956</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>040112</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-16.4109939</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-82490</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>040110</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-16.390434</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-82981</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>040112</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-16.4142869</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-214151</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-16.4149176</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-351531</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>040104</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-16.3751623</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-308096</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>040108</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-16.4458116</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-408834</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>040105</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CHARACATO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-16.4654124</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-329716</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>040107</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-16.4481823</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-329690</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-16.3970436</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-359854</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-16.4052496</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-479907</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>040122</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-16.4600118</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-315015</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>040108</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-16.6944388</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-469927</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-16.3970123</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-78078</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>040107</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-16.4484409</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-511933</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>040122</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-16.4688735</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-783960</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>040122</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-16.4579884</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-432161</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>040122</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-16.4672615</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-511951</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>040122</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-16.465198</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-84012</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-16.4094426</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-476749</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>040117</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>SACHACA</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-16.4245836</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-472982</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>040105</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CHARACATO</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-16.4764167</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-371242</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-16.4103957</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-474670</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>040101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-16.4192364</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-16978</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>040110</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-16.3926912</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-2444</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>040108</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-16.6224216</t>
@@ -2084,40 +1929,35 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>I-566968</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-16.3724328</t>
@@ -2136,40 +1976,35 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>I-408742</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-16.3959692</t>
@@ -2188,40 +2023,35 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>I-83927</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-16.3913501</t>
@@ -2240,40 +2070,35 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>I-2447</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>040108</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-16.6220388</t>
@@ -2292,40 +2117,35 @@
       <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>I-2437</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>040104</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-16.3865776</t>
@@ -2344,40 +2164,35 @@
       <c r="I37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>I-477887</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>040107</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-16.4384415</t>
@@ -2396,40 +2211,35 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>I-2448</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>040108</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-16.6217582</t>
@@ -2448,40 +2258,35 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>I-16980</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>040110</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-16.3933911</t>
@@ -2500,40 +2305,35 @@
       <c r="I40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>I-5468</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-16.4006537</t>
@@ -2552,11 +2352,6 @@
       <c r="I41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-464345</t>
+          <t>I-84012</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-16.4600496</t>
+          <t>-16.4094426</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-71.5566274</t>
+          <t>-71.5336615</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Paisajista / Calle 4</t>
+          <t>Avenida Independencia / Tabada</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-478443</t>
+          <t>I-83927</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-16.4603201</t>
+          <t>-16.3913501</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-71.5561759</t>
+          <t>-71.5431228</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Calle 4 / Calle s / n</t>
+          <t>Avenida Ejército / Avenida Emmel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-75854</t>
+          <t>I-82981</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.365769</t>
+          <t>-16.4142869</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-71.5243462</t>
+          <t>-71.5095311</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Francisco Mostajo / Calle Mariano Melgar</t>
+          <t>Calle Prolongación Avenida Jesús / Calle Industrial</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-76275</t>
+          <t>I-82490</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-16.417342</t>
+          <t>-16.390434</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-71.5833585</t>
+          <t>-71.5163236</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Progreso / Pasaje San Martín</t>
+          <t>Avenida Goyeneche / Calle Sánchez Trujillo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-77232</t>
+          <t>I-80956</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-16.3601947</t>
+          <t>-16.4109939</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-71.5626588</t>
+          <t>-71.5134547</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Tumbes / Sol Oeste</t>
+          <t>Avenida los Incas / Calle Malecón Paucarpata / Calle Victoria</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>José Galvez / Primavera / Reynoso</t>
+          <t>Primavera / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-80956</t>
+          <t>I-783960</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-16.4109939</t>
+          <t>-16.4579884</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-71.5134547</t>
+          <t>-71.5411931</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida los Incas / Calle Malecón Paucarpata / Calle Victoria / Prolongación Avenida Jesús</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-82490</t>
+          <t>I-78078</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-16.390434</t>
+          <t>-16.4484409</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-71.5163236</t>
+          <t>-71.5663707</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Goyeneche / Calle Sánchez Trujillo</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-82981</t>
+          <t>I-77232</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-16.4142869</t>
+          <t>-16.3601947</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-71.5095311</t>
+          <t>-71.5626588</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle Mariano Gonzales Prada / Prolongación Avenida Jesús</t>
+          <t>Avenida Tumbes / Sol Oeste</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-214151</t>
+          <t>I-76275</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-16.4149176</t>
+          <t>-16.417342</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-71.534333</t>
+          <t>-71.5833585</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Daniel Alcides Carrión / Calle San Rafael / Vía Exclusiva Daniel Alcides Carrión</t>
+          <t>Avenida Progreso / Pasaje San Martín</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-351531</t>
+          <t>I-75854</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-16.3751623</t>
+          <t>-16.365769</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-71.5577353</t>
+          <t>-71.5243462</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Calle s / n</t>
+          <t>Avenida Francisco Mostajo / Calle Mariano Melgar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-308096</t>
+          <t>I-566968</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-16.4458116</t>
+          <t>-16.3724328</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-71.8255575</t>
+          <t>-71.5337133</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida 28 de Julio / Calle s / n</t>
+          <t>Avenida Chilina / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1050,27 +1050,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-408834</t>
+          <t>I-5468</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-16.4654124</t>
+          <t>-16.4006537</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-71.4938768</t>
+          <t>-71.550931</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Characato / Calle s / n</t>
+          <t>Calle Los Jazmines / Las Orquídeas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1097,27 +1097,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-329716</t>
+          <t>I-511951</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-16.4481823</t>
+          <t>-16.465198</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-71.5661217</t>
+          <t>-71.5513946</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Paisajista / Calle s / n</t>
+          <t>Avenida Principal / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-329690</t>
+          <t>I-511933</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-16.3970436</t>
+          <t>-16.4688735</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-71.5411805</t>
+          <t>-71.5514302</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida de la Marina / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-359854</t>
+          <t>I-479907</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-16.4052496</t>
+          <t>-16.4600118</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-71.532842</t>
+          <t>-71.5469179</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez / Calle s / n</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-479907</t>
+          <t>I-478443</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-16.4600118</t>
+          <t>-16.4603201</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-71.5469179</t>
+          <t>-71.5561759</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Paisajista / Calle s / n</t>
+          <t>Calle 4 / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,27 +1285,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-315015</t>
+          <t>I-477887</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-16.6944388</t>
+          <t>-16.4384415</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-71.8806377</t>
+          <t>-71.5607491</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Las Américas / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-469927</t>
+          <t>I-476749</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-16.3970123</t>
+          <t>-16.4245836</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-71.5426428</t>
+          <t>-71.5873919</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida Zamacola / Calle Beaterio</t>
+          <t>Avenida Progreso / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1379,27 +1379,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-78078</t>
+          <t>I-474670</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-16.4484409</t>
+          <t>-16.4192364</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-71.5663707</t>
+          <t>-71.538601</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Avenida Paisajista / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-511933</t>
+          <t>I-472982</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-16.4688735</t>
+          <t>-16.4764167</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-71.5514302</t>
+          <t>-71.4922931</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-783960</t>
+          <t>I-469927</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-16.4579884</t>
+          <t>-16.3970123</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-71.5411931</t>
+          <t>-71.5426428</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Beaterio / Avenida Zamacola</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,27 +1520,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-432161</t>
+          <t>I-464345</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-16.4672615</t>
+          <t>-16.4600496</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-71.551416</t>
+          <t>-71.5566274</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle 1 / Calle s / n</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-511951</t>
+          <t>I-432161</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-16.465198</t>
+          <t>-16.4672615</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-71.5513946</t>
+          <t>-71.551416</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avenida Principal / Calle s / n</t>
+          <t>Calle 1 / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-84012</t>
+          <t>I-408834</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-16.4094426</t>
+          <t>-16.4654124</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-71.5336615</t>
+          <t>-71.4938768</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Tabada</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-476749</t>
+          <t>I-408742</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-16.4245836</t>
+          <t>-16.3959692</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-71.5873919</t>
+          <t>-71.5597961</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Avenida Progreso / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-472982</t>
+          <t>I-371242</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-16.4764167</t>
+          <t>-16.4103957</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-71.4922931</t>
+          <t>-71.5513085</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-371242</t>
+          <t>I-359854</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-16.4103957</t>
+          <t>-16.4052496</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-71.5513085</t>
+          <t>-71.532842</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-474670</t>
+          <t>I-351531</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-16.4192364</t>
+          <t>-16.3751623</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-71.538601</t>
+          <t>-71.5577353</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida Juan Vidaurrázaga / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,27 +1849,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-16978</t>
+          <t>I-329716</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-16.3926912</t>
+          <t>-16.4481823</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-71.5234521</t>
+          <t>-71.5661217</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Avenida Progreso / Calle Misti</t>
+          <t>Avenida Paisajista / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-2444</t>
+          <t>I-329690</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-16.6224216</t>
+          <t>-16.3970436</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-71.8765728</t>
+          <t>-71.5411805</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida de la Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1943,27 +1943,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-566968</t>
+          <t>I-315015</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-16.3724328</t>
+          <t>-16.6944388</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-71.5337133</t>
+          <t>-71.8806377</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Avenida Chilina / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1990,27 +1990,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-408742</t>
+          <t>I-308096</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-16.3959692</t>
+          <t>-16.4458116</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-71.5597961</t>
+          <t>-71.8255575</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida 28 de Julio / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2037,22 +2037,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-83927</t>
+          <t>I-2448</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-16.3913501</t>
+          <t>-16.6217582</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-71.5431228</t>
+          <t>-71.879947</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Avenida Ejército / Avenida Emmel</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-2437</t>
+          <t>I-2444</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-16.3865776</t>
+          <t>-16.6224216</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-71.5538504</t>
+          <t>-71.8765728</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Avenida Prolongación Ejército / Circunvalación</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-477887</t>
+          <t>I-2437</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-16.4384415</t>
+          <t>-16.3865776</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-71.5607491</t>
+          <t>-71.5538504</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Avenida Las Américas / Calle s / n</t>
+          <t>Avenida Prolongación Ejército / Circunvalación</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2225,27 +2225,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-2448</t>
+          <t>I-214151</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-16.6217582</t>
+          <t>-16.4149176</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-71.879947</t>
+          <t>-71.534333</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Daniel Alcides Carrión / Calle San Rafael</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2319,22 +2319,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I-5468</t>
+          <t>I-16978</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-16.4006537</t>
+          <t>-16.3926912</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-71.550931</t>
+          <t>-71.5234521</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Calle Los Jazmines / Las Orquídeas</t>
+          <t>Avenida Progreso / Calle Misti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
